--- a/Plantilla_Prime_OS_V7.xlsx
+++ b/Plantilla_Prime_OS_V7.xlsx
@@ -2731,7 +2731,7 @@
       <formula1>Listas!$C$2:$C$8</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>Listas!$E$2:$E$8</formula1>
+      <formula1>Listas!$E$2:$E$10</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>Listas!$A$2:$A$16</formula1>
@@ -8238,7 +8238,7 @@
       <formula1>Listas!$C$2:$C$8</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>Listas!$E$2:$E$8</formula1>
+      <formula1>Listas!$E$2:$E$10</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>Listas!$A$2:$A$16</formula1>
@@ -8945,6 +8945,11 @@
           <t>bíceps</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Complemento - Full Body A</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8952,6 +8957,11 @@
           <t>tríceps</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Complemento - Full Body B</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/Plantilla_Prime_OS_V7.xlsx
+++ b/Plantilla_Prime_OS_V7.xlsx
@@ -8947,7 +8947,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Complemento - Full Body A</t>
+          <t>Full Body A</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Complemento - Full Body B</t>
+          <t>Full Body B</t>
         </is>
       </c>
     </row>
